--- a/Hand_edited_log/1/student/anlpvhe187047/TC2/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/anlpvhe187047/TC2/GradeDetail.xlsx
@@ -1047,10 +1047,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>55747</x:v>
+        <x:v>51704</x:v>
       </x:c>
       <x:c r="Q2" s="0">
-        <x:v>4001</x:v>
+        <x:v>4002</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>46</x:v>
@@ -1103,10 +1103,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="0">
-        <x:v>4001</x:v>
+        <x:v>4002</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>55747</x:v>
+        <x:v>51704</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1159,10 +1159,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>55747</x:v>
+        <x:v>51704</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>4001</x:v>
+        <x:v>4002</x:v>
       </x:c>
       <x:c r="R4" s="2" t="s">
         <x:v>46</x:v>
@@ -1215,10 +1215,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>55747</x:v>
+        <x:v>51704</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>4001</x:v>
+        <x:v>4002</x:v>
       </x:c>
       <x:c r="R5" s="3" t="s">
         <x:v>56</x:v>
@@ -1271,10 +1271,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>4001</x:v>
+        <x:v>4002</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>55747</x:v>
+        <x:v>51704</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
         <x:v>56</x:v>
@@ -1327,10 +1327,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="P7" s="0">
-        <x:v>4001</x:v>
+        <x:v>4002</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>55747</x:v>
+        <x:v>51704</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
         <x:v>56</x:v>
@@ -1383,10 +1383,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>55747</x:v>
+        <x:v>51704</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>4001</x:v>
+        <x:v>4002</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1439,10 +1439,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>4001</x:v>
+        <x:v>4002</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>55747</x:v>
+        <x:v>51704</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>56</x:v>
@@ -1495,10 +1495,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>55747</x:v>
+        <x:v>51704</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>4001</x:v>
+        <x:v>4002</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
         <x:v>56</x:v>
@@ -1551,10 +1551,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>55747</x:v>
+        <x:v>51704</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>4001</x:v>
+        <x:v>4002</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
         <x:v>56</x:v>
@@ -1607,10 +1607,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P12" s="0">
-        <x:v>4001</x:v>
+        <x:v>4002</x:v>
       </x:c>
       <x:c r="Q12" s="0">
-        <x:v>55747</x:v>
+        <x:v>51704</x:v>
       </x:c>
       <x:c r="R12" s="3" t="s">
         <x:v>56</x:v>
